--- a/exports/BCA(AI)_Full_Report_April_2026.xlsx
+++ b/exports/BCA(AI)_Full_Report_April_2026.xlsx
@@ -27,14 +27,21 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A6B"/>
+        <bgColor rgb="001A3A6B"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,7 +58,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,6 +428,10 @@
   </sheetPr>
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
